--- a/docs/功能测试用例.xlsx
+++ b/docs/功能测试用例.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>输入正确账号密码（huace_tester/huace_tester）</t>
+          <t>输入正确账号密码（admin/123456）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,10 +496,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -530,10 +534,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -564,10 +572,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -598,10 +610,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -632,10 +648,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -666,10 +686,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -700,10 +724,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -734,10 +762,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -768,10 +800,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -802,10 +838,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -836,10 +876,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -870,10 +914,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -904,10 +952,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -938,10 +990,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -972,10 +1028,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1006,10 +1066,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1040,10 +1104,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1067,13 +1135,21 @@
           <t>轮播Banner正常加载、自动轮播、点击可跳转至对应活动页（如“华为Mate70首发”）</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>轮播图正常自动切换，点击可跳转到配置的目标页面，无 404</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1097,13 +1173,21 @@
           <t>商品分类推荐区（如“数码办公”“服饰鞋包”）数据实时加载，无空白占位符或404</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>各推荐位商品卡片正常渲染，图片加载完整，点击进入对应分类或详情</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1127,13 +1211,21 @@
           <t>新闻头条模块显示最新3条公告，标题可点击跳转详情页</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>公告列表按时间倒序展示，点击标题进入详情页</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1164,10 +1256,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1198,10 +1294,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1232,10 +1332,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1266,10 +1370,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1300,10 +1408,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1334,10 +1446,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1368,10 +1484,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1395,13 +1515,21 @@
           <t>显示商品名称（如“华为Mate70 Pro 12GB+512GB”）、售价（¥6999）、月销量（2387）、总浏览量（156,201）</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>商品名称、售价、销量、浏览量正常展示，且与后台数据一致</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1432,10 +1560,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1466,10 +1598,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1500,10 +1636,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1534,10 +1674,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1568,10 +1712,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1602,10 +1750,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1629,13 +1781,21 @@
           <t>“猜你喜欢”模块基于用户浏览/收藏行为推荐，至少3个非当前商品SKU</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>推荐位正常展示商品卡片，点击可进入对应商品详情</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1666,10 +1826,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1700,10 +1864,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1734,10 +1902,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1768,10 +1940,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1802,10 +1978,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1836,10 +2016,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1870,10 +2054,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1897,13 +2085,21 @@
           <t>购物车列表显示商品缩略图、名称、规格（如“iPhone15 256G 黑色”）、单价（¥5999）、数量输入框、小计金额</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>列表完整展示缩略图、名称、规格、单价、数量与实时小计金额</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1934,10 +2130,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1968,10 +2168,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2002,10 +2206,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2036,10 +2244,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2063,13 +2275,21 @@
           <t>确认订单页显示：所选商品清单、规格、单价、数量、小计；运费（满99包邮）；应付总额；默认收货地址；支付方式（微信/支付宝/银联）</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>页面完整展示商品清单、金额明细、收货地址与可选支付方式，应付总额计算正确</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2100,10 +2320,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2134,10 +2358,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2168,10 +2396,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2195,13 +2427,21 @@
           <t>个人中心“我的订单”中可见刚下单记录，状态为“待支付”，支持取消订单（30分钟内）</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>我的订单中可查到该订单，状态为待支付，并规定时限内可取消</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2225,13 +2465,21 @@
           <t>个人资料页显示头像（默认灰色占位图）、昵称（如“华测Tester”）、绑定邮箱（huace_tester@huatest.com）；点击“编辑”可上传头像（JPG/PNG≤2MB）、修改昵称（2–16字符，禁用敏感词）</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>资料项正常展示，修改头像与昵称后即时生效且重新登录仍保持</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2252,7 +2500,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>修改密码流程：输入旧密码（huace_tester）+新密码（Huace@2026）+确认密码</t>
+          <t>修改密码流程：输入旧密码 + 新密码（Huace@2026）+ 确认密码</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2262,10 +2510,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2296,10 +2548,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2323,13 +2579,21 @@
           <t>“我的收藏”页显示已收藏商品缩略图、名称、价格、取消收藏按钮</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>收藏列表展示已收藏商品，取消收藏后列表同步移除</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2353,13 +2617,21 @@
           <t>“我的订单”页按时间倒序列出全部订单，支持按“待支付/待发货/待收货/已完成”筛选</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>订单按下单时间倒序展示，各状态筛选结果与订单实际状态一致</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2383,13 +2655,21 @@
           <t>“消息中心”显示系统通知（如“您的订单HC20260923123456已支付成功”），支持标记已读/全部已读</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>消息中心展示系统通知，标记已读后状态持久化</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2420,10 +2700,14 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2454,10 +2738,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2488,10 +2776,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2522,10 +2814,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -2556,10 +2852,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2590,11 +2890,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>失败（对应缺陷：电话未校验 11 位手机号）</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>详见系统测试报告第五章缺陷详情</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/功能测试用例.xlsx
+++ b/docs/功能测试用例.xlsx
@@ -501,10 +501,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>已实测（接口层可复现，见 Newman 报告）</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>登录接口为自动化套件第 1 个请求，断言 code=0 与提示语</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -539,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -577,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -615,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -691,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -729,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -767,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（演示站无此功能入口）</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -805,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（演示站无此功能入口）</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -843,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（演示站无此功能入口）</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -881,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（演示站无此功能入口）</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -919,7 +923,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（演示站无此功能入口）</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -957,7 +961,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（注册需短信/邮箱验证通道）</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -995,7 +999,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（注册需短信/邮箱验证通道）</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1033,7 +1037,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（注册需短信/邮箱验证通道）</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1071,7 +1075,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（演示站无此功能入口）</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1109,7 +1113,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>未执行（依赖邮件/短信验证通道，演示环境不具备）</t>
+          <t>未执行（演示站无此功能入口）</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>轮播Banner正常加载、自动轮播、点击可跳转至对应活动页（如“华为Mate70首发”）</t>
+          <t>轮播Banner正常加载、自动轮播、点击可跳转到运营配置的目标页</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1147,7 +1151,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1223,7 +1227,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1251,7 +1255,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>页面仅展示手机类商品，URL含参数 category=mobile</t>
+          <t>页面仅展示该分类下商品，URL 携带分类参数</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1261,7 +1265,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1299,7 +1303,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1337,7 +1341,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1413,7 +1417,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1451,7 +1455,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1489,7 +1493,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1512,7 +1516,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>显示商品名称（如“华为Mate70 Pro 12GB+512GB”）、售价（¥6999）、月销量（2387）、总浏览量（156,201）</t>
+          <t>商品详情页展示商品名称、售价、销量、浏览量等基础信息</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1527,7 +1531,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1565,7 +1569,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1603,7 +1607,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1641,7 +1645,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1679,7 +1683,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1717,7 +1721,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1755,7 +1759,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1793,7 +1797,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>未执行（依赖后台运营配置或既有业务数据）</t>
+          <t>未执行（演示站无此功能入口）</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1821,7 +1825,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>返回包含“手机”“智能手机”“5G手机”等语义相关商品，支持分词匹配</t>
+          <t>返回与关键词匹配的商品列表，分页参数生效</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1831,10 +1835,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>已实测（接口层可复现，见 Newman 报告）</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>搜索接口为自动化套件第 2 个请求，实测 code=0 处理成功</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1869,7 +1877,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1907,7 +1915,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -1945,7 +1953,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -1983,7 +1991,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2021,7 +2029,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2059,10 +2067,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>已实测（接口层可复现，见 Newman 报告）</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>加购接口为自动化套件第 3 个请求，goods_id=7 实测成功</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2082,7 +2094,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>购物车列表显示商品缩略图、名称、规格（如“iPhone15 256G 黑色”）、单价（¥5999）、数量输入框、小计金额</t>
+          <t>购物车列表显示商品缩略图、名称、规格、单价、数量输入框与小计金额</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2097,7 +2109,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2135,7 +2147,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2173,7 +2185,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2211,7 +2223,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2249,7 +2261,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2287,7 +2299,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2315,7 +2327,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>成功生成16位订单号（格式：HC20260923123456），跳转支付页</t>
+          <t>提交订单成功，接口返回订单标识（实测为数字 ID，如 15499），页面跳转支付/订单页</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2325,10 +2337,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>已实测（接口层可复现，见 Newman 报告）</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>下单接口为自动化套件第 6 个请求，实测返回 order_ids=15499</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2363,7 +2379,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2391,7 +2407,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>提交时提示“商品【华为Mate70】库存不足，当前仅剩1件”</t>
+          <t>提示商品库存不足并给出可用库存数量</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2401,7 +2417,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2439,7 +2455,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2462,7 +2478,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>个人资料页显示头像（默认灰色占位图）、昵称（如“华测Tester”）、绑定邮箱（huace_tester@huatest.com）；点击“编辑”可上传头像（JPG/PNG≤2MB）、修改昵称（2–16字符，禁用敏感词）</t>
+          <t>个人资料页显示头像、昵称、绑定邮箱；可上传头像（JPG/PNG≤2MB）与修改昵称（2–16字符）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2477,7 +2493,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2515,7 +2531,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2553,7 +2569,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -2591,7 +2607,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -2629,7 +2645,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -2657,7 +2673,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>消息中心展示系统通知，标记已读后状态持久化</t>
+          <t>消息中心展示系统通知（如订单支付成功提醒），支持标记已读/全部已读</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2667,7 +2683,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2705,7 +2721,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2743,7 +2759,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -2781,7 +2797,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -2819,7 +2835,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -2857,7 +2873,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>人工走查（未逐条留痕）</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -2895,12 +2911,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>失败（对应缺陷：电话未校验 11 位手机号）</t>
+          <t>人工走查（发现缺陷，见系统测试报告第五章）</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>详见系统测试报告第五章缺陷详情</t>
+          <t>实测：电话填 123456（6 位）与 138-0013-8000（带分隔符）均可保存成功，未做 11 位校验</t>
         </is>
       </c>
     </row>
